--- a/generated/spreadsheet/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area.xlsx
+++ b/generated/spreadsheet/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I109"/>
+  <dimension ref="A1:I108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -568,14 +568,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application sub type</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Further classification of the application type for specific variations within the main application type</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -599,19 +599,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Submission date</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>Date the application is submitted in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -630,19 +630,19 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Modules[]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>List of required modules for this application that can be used to validate the application</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -661,14 +661,18 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+          <t>Documents[]</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -697,13 +701,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -732,13 +736,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -748,7 +752,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -767,23 +771,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -802,18 +806,18 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Uploaded date</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -837,23 +841,27 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Base64</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -877,12 +885,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Base64</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -892,7 +900,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -916,12 +924,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -931,7 +939,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -955,17 +963,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>File size</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -984,22 +992,18 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>File size</t>
-        </is>
-      </c>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1009,7 +1013,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1028,13 +1032,13 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1063,48 +1067,48 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Transactions[]</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Transactions[]</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1114,32 +1118,28 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1163,14 +1163,18 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1180,7 +1184,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1199,18 +1203,18 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1220,51 +1224,47 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1272,14 +1272,18 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1289,7 +1293,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1308,13 +1312,13 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1324,7 +1328,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1343,13 +1347,13 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1378,13 +1382,13 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1413,13 +1417,13 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1429,32 +1433,32 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="2" t="n"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1464,32 +1468,28 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1513,14 +1513,18 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1530,7 +1534,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1549,18 +1553,18 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1570,51 +1574,47 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1622,14 +1622,18 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1639,7 +1643,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1658,13 +1662,13 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1674,7 +1678,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1693,13 +1697,13 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1728,13 +1732,13 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1763,13 +1767,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1779,7 +1783,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1793,18 +1797,14 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1828,19 +1828,19 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -1850,63 +1850,63 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>User role</t>
-        </is>
-      </c>
+          <t>Biodiversity gain condition applies</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition applies</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
+          <t>Biodiversity gain condition exemption reason[]</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Exemption type</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
+          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -1925,19 +1925,19 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Exemption type</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
+          <t>The reason the exemption applies to this proposal</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -1951,24 +1951,24 @@
       <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
+          <t>Biodiversity net gain details</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Pre development date</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>The reason the exemption applies to this proposal</t>
+          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -1987,19 +1987,19 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Pre development date</t>
+          <t>Pre development biodiversity value</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
+          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2018,24 +2018,24 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Pre development biodiversity value</t>
+          <t>Earlier date reason</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
+          <t>Reason for using a pre-development date that is earlier than the application submission</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2049,19 +2049,19 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Earlier date reason</t>
+          <t>Habitat loss after 2020</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Reason for using a pre-development date that is earlier than the application submission</t>
+          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2080,24 +2080,28 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss after 2020</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Loss date</t>
+        </is>
+      </c>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
+          <t>Date the activity causing habitat loss or degradation occurred</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2116,18 +2120,18 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Loss date</t>
+          <t>Pre loss biodiversity value</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Date the activity causing habitat loss or degradation occurred</t>
+          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2151,23 +2155,23 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Pre loss biodiversity value</t>
+          <t>Supporting evidence</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
+          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2181,28 +2185,24 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>Supporting evidence</t>
-        </is>
-      </c>
+          <t>Metric publication date</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
+          <t>Publication date of the biodiversity metric tool used for calculations</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2216,19 +2216,19 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Metric publication date</t>
+          <t>Irreplaceable habitats</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Publication date of the biodiversity metric tool used for calculations</t>
+          <t>Indicates whether the site contains any irreplaceable habitats</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2247,24 +2247,24 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats</t>
+          <t>Irreplaceable habitats details</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether the site contains any irreplaceable habitats</t>
+          <t>Description and references for any irreplaceable habitats identified on the site</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2278,14 +2278,18 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats details</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Description and references for any irreplaceable habitats identified on the site</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2295,32 +2299,32 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n"/>
-      <c r="B55" s="2" t="n"/>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>National requirement types[]</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2337,17 +2341,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Community consultation</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>What community consultation activities have taken place as part of the application</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Have consulted</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -2355,12 +2359,12 @@
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Whether community consultation has been carried out</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2370,19 +2374,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Community consultation</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>What community consultation activities have taken place as part of the application</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Have consulted</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
@@ -2390,26 +2386,34 @@
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Whether community consultation has been carried out</t>
+          <t>Provide details of the community consultation</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="2" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -2417,34 +2421,26 @@
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Provide details of the community consultation</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Conflict person name</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
@@ -2452,17 +2448,17 @@
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2467,7 @@
       <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
@@ -2479,7 +2475,7 @@
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2494,11 +2490,19 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n"/>
-      <c r="B61" s="2" t="n"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -2506,7 +2510,7 @@
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>A name of a person</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2516,24 +2520,16 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
@@ -2541,12 +2537,12 @@
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2560,7 +2556,7 @@
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
@@ -2568,12 +2564,12 @@
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -2583,11 +2579,19 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="2" t="n"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Demolition reason</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Why demolition is necessary at the development site</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
@@ -2595,7 +2599,7 @@
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Why is it necessary to demolish all or part of the building(s) and structure(s)?</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -2612,17 +2616,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Demolition reason</t>
+          <t>Ownership certificates and agricultural land declaration</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Why demolition is necessary at the development site</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Sole owner</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -2630,12 +2634,12 @@
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Why is it necessary to demolish all or part of the building(s) and structure(s)?</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -2645,19 +2649,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Agricultural tenants</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -2665,7 +2661,7 @@
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -2684,25 +2680,33 @@
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr"/>
-      <c r="E67" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2721,13 +2725,13 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -2737,7 +2741,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2756,13 +2760,13 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -2791,13 +2795,13 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -2826,13 +2830,13 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -2842,7 +2846,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2856,23 +2860,19 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Notice date</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -2886,24 +2886,20 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Notice date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -2917,15 +2913,19 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2949,19 +2949,19 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Publication date</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -2975,29 +2975,25 @@
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3002,7 @@
       <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
+          <t>Applicant signature</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
@@ -3014,12 +3010,12 @@
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Digital signature of the applicant</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -3033,7 +3029,7 @@
       <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
+          <t>Agent signature</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -3041,7 +3037,7 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Digital signature of the agent (if applicable)</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3060,7 +3056,7 @@
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -3068,7 +3064,7 @@
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -3083,11 +3079,19 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n"/>
-      <c r="B80" s="2" t="n"/>
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
@@ -3095,34 +3099,26 @@
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="n"/>
+      <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
@@ -3130,17 +3126,17 @@
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3145,7 @@
       <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -3157,7 +3153,7 @@
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -3176,7 +3172,7 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
@@ -3184,7 +3180,7 @@
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -3203,7 +3199,7 @@
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
@@ -3211,7 +3207,7 @@
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -3226,11 +3222,19 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n"/>
-      <c r="B85" s="2" t="n"/>
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
@@ -3238,7 +3242,7 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -3248,24 +3252,16 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
@@ -3273,12 +3269,12 @@
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -3292,7 +3288,7 @@
       <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
@@ -3300,17 +3296,17 @@
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3315,7 @@
       <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
@@ -3327,17 +3323,17 @@
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3342,7 @@
       <c r="B89" s="2" t="n"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
@@ -3354,26 +3350,34 @@
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n"/>
-      <c r="B90" s="2" t="n"/>
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Related applications</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Details of any other development proposals made for the site</t>
+        </is>
+      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Has related applications</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
@@ -3381,47 +3385,43 @@
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Are there any related applications, previous proposals or demolitions for the site</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Related applications</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>Details of any other development proposals made for the site</t>
-        </is>
-      </c>
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Has related applications</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr"/>
+          <t>Related applications[]</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Are there any related applications, previous proposals or demolitions for the site</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -3440,14 +3440,14 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>A description of the related application</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>A description of the related application</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -3488,33 +3488,41 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n"/>
-      <c r="B94" s="2" t="n"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Decision date</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -3524,16 +3532,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A95" s="2" t="n"/>
+      <c r="B95" s="2" t="n"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -3541,19 +3541,19 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -3572,14 +3572,14 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -3603,19 +3603,19 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -3634,14 +3634,14 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -3665,14 +3665,14 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -3696,14 +3696,14 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -3727,19 +3727,19 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -3758,14 +3758,14 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -3780,50 +3780,46 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n"/>
-      <c r="B103" s="2" t="n"/>
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A104" s="2" t="n"/>
+      <c r="B104" s="2" t="n"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr"/>
@@ -3831,12 +3827,12 @@
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -3850,7 +3846,7 @@
       <c r="B105" s="2" t="n"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
@@ -3858,17 +3854,17 @@
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3877,15 +3873,19 @@
       <c r="B106" s="2" t="n"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3909,14 +3909,14 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -3940,14 +3940,14 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -3956,37 +3956,6 @@
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="n"/>
-      <c r="B109" s="2" t="n"/>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr"/>
-      <c r="F109" s="2" t="inlineStr"/>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -3994,40 +3963,40 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B65"/>
-    <mergeCell ref="A34:A41"/>
-    <mergeCell ref="A42:A55"/>
-    <mergeCell ref="A24:A29"/>
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A95:A103"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="A66:A80"/>
-    <mergeCell ref="A81:A85"/>
-    <mergeCell ref="B95:B103"/>
-    <mergeCell ref="B59:B61"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="B56"/>
-    <mergeCell ref="A91:A94"/>
-    <mergeCell ref="A65"/>
-    <mergeCell ref="B81:B85"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="A104:A109"/>
-    <mergeCell ref="B24:B29"/>
-    <mergeCell ref="A56"/>
-    <mergeCell ref="B86:B90"/>
-    <mergeCell ref="B34:B41"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B42:B55"/>
-    <mergeCell ref="B66:B80"/>
-    <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B91:B94"/>
-    <mergeCell ref="A86:A90"/>
-    <mergeCell ref="B104:B109"/>
+    <mergeCell ref="B64"/>
+    <mergeCell ref="B55"/>
+    <mergeCell ref="A85:A89"/>
+    <mergeCell ref="A103:A108"/>
+    <mergeCell ref="B2:B18"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A65:A79"/>
+    <mergeCell ref="A64"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="B41:B54"/>
+    <mergeCell ref="B80:B84"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="B85:B89"/>
+    <mergeCell ref="B23:B28"/>
+    <mergeCell ref="B65:B79"/>
+    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="B103:B108"/>
+    <mergeCell ref="B94:B102"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="A33:A40"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="A23:A28"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="A94:A102"/>
+    <mergeCell ref="A55"/>
+    <mergeCell ref="A41:A54"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="B33:B40"/>
+    <mergeCell ref="A80:A84"/>
+    <mergeCell ref="B90:B93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area.xlsx
+++ b/generated/spreadsheet/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area.xlsx
@@ -3483,7 +3483,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">

--- a/generated/spreadsheet/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area.xlsx
+++ b/generated/spreadsheet/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area.xlsx
@@ -2569,7 +2569,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">

--- a/generated/spreadsheet/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area.xlsx
+++ b/generated/spreadsheet/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -491,29 +491,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Submission reference</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A unique reference for the submission</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -532,7 +532,7 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -563,19 +563,19 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Specification profile</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>The specification profile used to determine context-specific allowed codelist values for the application</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -594,24 +594,24 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -625,24 +625,24 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
+          <t>Submitted at</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>The date and time the application was submitted</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -656,28 +656,24 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Created at</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The date and time the submission payload was created</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -691,7 +687,7 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -701,13 +697,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -726,7 +722,7 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -736,13 +732,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -752,7 +748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -761,7 +757,7 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -771,23 +767,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -796,7 +792,7 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -806,18 +802,18 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -831,7 +827,7 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -841,27 +837,23 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Base64</t>
-        </is>
-      </c>
+          <t>Uploaded date</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -870,7 +862,7 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -885,12 +877,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Base64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -900,7 +892,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -909,7 +901,7 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -924,12 +916,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -939,7 +931,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -948,7 +940,7 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -963,17 +955,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>File size</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -987,33 +979,37 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
+          <t>Documents[]</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>File size</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1018,7 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1032,18 +1028,18 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1057,7 +1053,7 @@
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1067,48 +1063,48 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Transactions[]</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>Submission details</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Transactions[]</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1118,28 +1114,32 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1163,18 +1163,14 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1184,7 +1180,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1203,18 +1199,18 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1224,47 +1220,51 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1272,18 +1272,14 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1293,7 +1289,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1312,13 +1308,13 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1328,7 +1324,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1347,13 +1343,13 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1382,13 +1378,13 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1417,13 +1413,13 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1433,32 +1429,32 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr"/>
-      <c r="E29" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1468,28 +1464,32 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1513,18 +1513,14 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1534,7 +1530,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1553,18 +1549,18 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1574,47 +1570,51 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n"/>
-      <c r="B34" s="2" t="n"/>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1622,18 +1622,14 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1643,7 +1639,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1662,13 +1658,13 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1678,7 +1674,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1697,13 +1693,13 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1732,13 +1728,13 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1767,13 +1763,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1783,7 +1779,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1797,14 +1793,18 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1828,19 +1828,19 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -1850,63 +1850,63 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition applies</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="2" t="n"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Exemption type</t>
-        </is>
-      </c>
+          <t>Biodiversity gain condition applies</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
+          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -1925,19 +1925,19 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Exemption type</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>The reason the exemption applies to this proposal</t>
+          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -1951,24 +1951,24 @@
       <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Pre development date</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
+          <t>The reason the exemption applies to this proposal</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -1987,19 +1987,19 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Pre development biodiversity value</t>
+          <t>Pre development date</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
+          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2018,24 +2018,24 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Earlier date reason</t>
+          <t>Pre development biodiversity value</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Reason for using a pre-development date that is earlier than the application submission</t>
+          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2049,19 +2049,19 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss after 2020</t>
+          <t>Earlier date reason</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
+          <t>Reason for using a pre-development date that is earlier than the application submission</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2080,28 +2080,24 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Loss date</t>
-        </is>
-      </c>
+          <t>Habitat loss after 2020</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Date the activity causing habitat loss or degradation occurred</t>
+          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2120,18 +2116,18 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Pre loss biodiversity value</t>
+          <t>Loss date</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
+          <t>Date the activity causing habitat loss or degradation occurred</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2155,23 +2151,23 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Supporting evidence</t>
+          <t>Pre loss biodiversity value</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
+          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2185,24 +2181,28 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Metric publication date</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Supporting evidence</t>
+        </is>
+      </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Publication date of the biodiversity metric tool used for calculations</t>
+          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2216,19 +2216,19 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats</t>
+          <t>Metric publication date</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether the site contains any irreplaceable habitats</t>
+          <t>Publication date of the biodiversity metric tool used for calculations</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2247,24 +2247,24 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats details</t>
+          <t>Irreplaceable habitats</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Description and references for any irreplaceable habitats identified on the site</t>
+          <t>Indicates whether the site contains any irreplaceable habitats</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2278,18 +2278,14 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Irreplaceable habitats details</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Description and references for any irreplaceable habitats identified on the site</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2299,32 +2295,32 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr"/>
-      <c r="E55" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2341,17 +2337,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Community consultation</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>What community consultation activities have taken place as part of the application</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Have consulted</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -2359,12 +2355,12 @@
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Whether community consultation has been carried out</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2374,11 +2370,19 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n"/>
-      <c r="B57" s="2" t="n"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Community consultation</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>What community consultation activities have taken place as part of the application</t>
+        </is>
+      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Have consulted</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
@@ -2386,34 +2390,26 @@
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Provide details of the community consultation</t>
+          <t>Whether community consultation has been carried out</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="n"/>
+      <c r="B58" s="2" t="n"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -2421,26 +2417,34 @@
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Provide details of the community consultation</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n"/>
-      <c r="B59" s="2" t="n"/>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
@@ -2448,17 +2452,17 @@
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2471,7 @@
       <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
@@ -2475,7 +2479,7 @@
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2490,19 +2494,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="n"/>
+      <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -2510,7 +2506,7 @@
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2520,16 +2516,24 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n"/>
-      <c r="B62" s="2" t="n"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
@@ -2537,12 +2541,12 @@
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2556,7 +2560,7 @@
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
@@ -2564,12 +2568,12 @@
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -2579,19 +2583,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Demolition reason</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Why demolition is necessary at the development site</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
@@ -2599,12 +2595,12 @@
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Why is it necessary to demolish all or part of the building(s) and structure(s)?</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -2616,17 +2612,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificates and agricultural land declaration</t>
+          <t>Demolition reason</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Why demolition is necessary at the development site</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -2634,12 +2630,12 @@
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Why is it necessary to demolish all or part of the building(s) and structure(s)?</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -2649,11 +2645,19 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n"/>
-      <c r="B66" s="2" t="n"/>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+        </is>
+      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
+          <t>Sole owner</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -2661,7 +2665,7 @@
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -2680,33 +2684,25 @@
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Agricultural tenants</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2725,13 +2721,13 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -2741,7 +2737,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2760,13 +2756,13 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -2795,13 +2791,13 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -2830,13 +2826,13 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -2846,7 +2842,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2860,19 +2856,23 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Notice date</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -2886,20 +2886,24 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Notice served date</t>
+        </is>
+      </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -2913,29 +2917,25 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Newspaper name</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2944,29 +2944,25 @@
       <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2975,25 +2971,29 @@
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3002,25 +3002,29 @@
       <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3033,7 @@
       <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -3037,7 +3041,7 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3047,7 +3051,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3060,7 @@
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -3064,34 +3068,26 @@
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A80" s="2" t="n"/>
+      <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
@@ -3099,12 +3095,12 @@
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -3114,11 +3110,19 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n"/>
-      <c r="B81" s="2" t="n"/>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
@@ -3126,17 +3130,17 @@
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3149,7 @@
       <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -3153,7 +3157,7 @@
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -3172,7 +3176,7 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
@@ -3180,12 +3184,12 @@
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -3199,7 +3203,7 @@
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
@@ -3207,12 +3211,12 @@
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -3222,19 +3226,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
@@ -3242,7 +3238,7 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -3252,16 +3248,24 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n"/>
-      <c r="B86" s="2" t="n"/>
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
@@ -3269,12 +3273,12 @@
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -3288,7 +3292,7 @@
       <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
@@ -3296,17 +3300,17 @@
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3319,7 @@
       <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
@@ -3323,17 +3327,17 @@
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3346,7 @@
       <c r="B89" s="2" t="n"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
@@ -3350,34 +3354,26 @@
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>Related applications</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Details of any other development proposals made for the site</t>
-        </is>
-      </c>
+      <c r="A90" s="2" t="n"/>
+      <c r="B90" s="2" t="n"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Has related applications</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
@@ -3385,43 +3381,47 @@
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Are there any related applications, previous proposals or demolitions for the site</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n"/>
-      <c r="B91" s="2" t="n"/>
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Related applications</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Details of any other development proposals made for the site</t>
+        </is>
+      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Has related applications</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>Are there any related applications, previous proposals or demolitions for the site</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -3440,14 +3440,14 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>A description of the related application</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -3471,58 +3471,50 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Decision date</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>A description of the related application</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related applications[]</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -3532,8 +3524,16 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n"/>
-      <c r="B95" s="2" t="n"/>
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -3541,19 +3541,19 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -3572,14 +3572,14 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -3603,19 +3603,19 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -3634,19 +3634,19 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -3665,19 +3665,19 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -3696,19 +3696,19 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -3727,19 +3727,19 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -3758,14 +3758,14 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>A text description providing details about the subject.</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -3780,46 +3780,50 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="n"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n"/>
-      <c r="B104" s="2" t="n"/>
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Site seen from public area</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr"/>
@@ -3827,12 +3831,12 @@
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -3846,7 +3850,7 @@
       <c r="B105" s="2" t="n"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
@@ -3854,17 +3858,17 @@
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3873,19 +3877,15 @@
       <c r="B106" s="2" t="n"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr"/>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3909,14 +3909,14 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Full name</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -3940,22 +3940,53 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -3963,40 +3994,40 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B64"/>
-    <mergeCell ref="B55"/>
-    <mergeCell ref="A85:A89"/>
-    <mergeCell ref="A103:A108"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A65:A79"/>
-    <mergeCell ref="A64"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="B41:B54"/>
-    <mergeCell ref="B80:B84"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="B85:B89"/>
-    <mergeCell ref="B23:B28"/>
-    <mergeCell ref="B65:B79"/>
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="B103:B108"/>
-    <mergeCell ref="B94:B102"/>
-    <mergeCell ref="A29:A32"/>
-    <mergeCell ref="A33:A40"/>
-    <mergeCell ref="A61:A63"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="A23:A28"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="A94:A102"/>
-    <mergeCell ref="A55"/>
-    <mergeCell ref="A41:A54"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="B33:B40"/>
-    <mergeCell ref="A80:A84"/>
-    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="B65"/>
+    <mergeCell ref="A34:A41"/>
+    <mergeCell ref="A42:A55"/>
+    <mergeCell ref="A24:A29"/>
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A95:A103"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="A66:A80"/>
+    <mergeCell ref="A81:A85"/>
+    <mergeCell ref="B95:B103"/>
+    <mergeCell ref="B59:B61"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="B56"/>
+    <mergeCell ref="A91:A94"/>
+    <mergeCell ref="A65"/>
+    <mergeCell ref="B81:B85"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A104:A109"/>
+    <mergeCell ref="B24:B29"/>
+    <mergeCell ref="A56"/>
+    <mergeCell ref="B86:B90"/>
+    <mergeCell ref="B34:B41"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B42:B55"/>
+    <mergeCell ref="B66:B80"/>
+    <mergeCell ref="B2:B19"/>
+    <mergeCell ref="B91:B94"/>
+    <mergeCell ref="A86:A90"/>
+    <mergeCell ref="B104:B109"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area.xlsx
+++ b/generated/spreadsheet/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I109"/>
+  <dimension ref="A1:I112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -435,9 +435,9 @@
     <col width="48" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -1413,13 +1413,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1448,13 +1452,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1469,58 +1477,66 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Unique Property Reference Number for a property</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Agent contact details</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Agent reference</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>A reference to an agent object</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+      <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1530,7 +1546,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1544,18 +1560,14 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1565,7 +1577,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1584,18 +1596,18 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -1605,47 +1617,51 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1653,18 +1669,14 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1674,7 +1686,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1693,13 +1705,13 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1709,7 +1721,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1728,13 +1740,13 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1763,13 +1775,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1798,13 +1810,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr"/>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1814,7 +1830,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1844,22 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1859,19 +1883,27 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -1881,37 +1913,33 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition applies</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1920,19 +1948,19 @@
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Exemption type</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -1942,33 +1970,37 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
+          <t>Biodiversity gain condition applies</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>The reason the exemption applies to this proposal</t>
+          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -1982,24 +2014,24 @@
       <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Pre development date</t>
+          <t>Exemption type</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
+          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2013,24 +2045,24 @@
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Pre development biodiversity value</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
+          <t>The reason the exemption applies to this proposal</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2049,24 +2081,24 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Earlier date reason</t>
+          <t>Pre development date</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Reason for using a pre-development date that is earlier than the application submission</t>
+          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2080,24 +2112,24 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss after 2020</t>
+          <t>Pre development biodiversity value</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
+          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2111,28 +2143,24 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Loss date</t>
-        </is>
-      </c>
+          <t>Earlier date reason</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Date the activity causing habitat loss or degradation occurred</t>
+          <t>Reason for using a pre-development date that is earlier than the application submission</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2146,28 +2174,24 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Pre loss biodiversity value</t>
-        </is>
-      </c>
+          <t>Habitat loss after 2020</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
+          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2186,23 +2210,23 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Supporting evidence</t>
+          <t>Loss date</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
+          <t>Date the activity causing habitat loss or degradation occurred</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2216,19 +2240,23 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Metric publication date</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Pre loss biodiversity value</t>
+        </is>
+      </c>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Publication date of the biodiversity metric tool used for calculations</t>
+          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2247,24 +2275,28 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Supporting evidence</t>
+        </is>
+      </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether the site contains any irreplaceable habitats</t>
+          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2278,24 +2310,24 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats details</t>
+          <t>Metric publication date</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Description and references for any irreplaceable habitats identified on the site</t>
+          <t>Publication date of the biodiversity metric tool used for calculations</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2309,23 +2341,19 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Irreplaceable habitats</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Indicates whether the site contains any irreplaceable habitats</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2335,27 +2363,23 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Irreplaceable habitats details</t>
+        </is>
+      </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Description and references for any irreplaceable habitats identified on the site</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2365,37 +2389,37 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Community consultation</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>What community consultation activities have taken place as part of the application</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Have consulted</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr"/>
-      <c r="E57" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Whether community consultation has been carried out</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -2405,11 +2429,19 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="2" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -2417,7 +2449,7 @@
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Provide details of the community consultation</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2427,24 +2459,24 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Conflict of interest</t>
+          <t>Community consultation</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>What community consultation activities have taken place as part of the application</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Have consulted</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
@@ -2452,7 +2484,7 @@
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Whether community consultation has been carried out</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2471,7 +2503,7 @@
       <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
@@ -2479,7 +2511,7 @@
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Reference to the applicant or agent with the conflict</t>
+          <t>Provide details of the community consultation</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2494,11 +2526,19 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n"/>
-      <c r="B61" s="2" t="n"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -2506,31 +2546,23 @@
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Person reference</t>
@@ -2541,7 +2573,7 @@
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -2551,7 +2583,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2592,7 @@
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
@@ -2568,26 +2600,34 @@
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="2" t="n"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
@@ -2595,12 +2635,12 @@
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -2610,19 +2650,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Demolition reason</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Why demolition is necessary at the development site</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -2630,12 +2662,12 @@
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Why is it necessary to demolish all or part of the building(s) and structure(s)?</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -2645,19 +2677,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -2665,12 +2689,12 @@
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -2680,11 +2704,19 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="2" t="n"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Demolition reason</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Why demolition is necessary at the development site</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -2692,12 +2724,12 @@
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>Why is it necessary to demolish all or part of the building(s) and structure(s)?</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -2707,37 +2739,37 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2746,28 +2778,20 @@
       <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
+          <t>Agricultural tenants</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -2791,13 +2815,13 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -2807,7 +2831,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2826,13 +2850,13 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -2861,13 +2885,13 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -2877,7 +2901,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2891,24 +2915,32 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Notice served date</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2917,20 +2949,32 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr"/>
-      <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -2944,15 +2988,27 @@
       <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr"/>
-      <c r="E75" s="2" t="inlineStr"/>
-      <c r="F75" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -2971,29 +3027,29 @@
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
+          <t>Owners and tenants[]</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Notice served date</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3002,29 +3058,25 @@
       <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3085,7 @@
       <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Steps taken</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -3041,7 +3093,7 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3051,7 +3103,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3060,20 +3112,24 @@
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -3087,15 +3143,19 @@
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -3110,19 +3170,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="n"/>
+      <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
@@ -3130,12 +3182,12 @@
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -3149,7 +3201,7 @@
       <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -3157,17 +3209,17 @@
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3228,7 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
@@ -3184,26 +3236,34 @@
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n"/>
-      <c r="B84" s="2" t="n"/>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
@@ -3211,17 +3271,17 @@
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3290,7 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
@@ -3238,7 +3298,7 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -3253,19 +3313,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
@@ -3273,7 +3325,7 @@
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -3283,7 +3335,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3344,7 @@
       <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
@@ -3300,17 +3352,17 @@
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3371,7 @@
       <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
@@ -3327,12 +3379,12 @@
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -3342,11 +3394,19 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n"/>
-      <c r="B89" s="2" t="n"/>
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
@@ -3354,12 +3414,12 @@
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -3373,7 +3433,7 @@
       <c r="B90" s="2" t="n"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
@@ -3381,34 +3441,26 @@
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Related applications</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>Details of any other development proposals made for the site</t>
-        </is>
-      </c>
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Has related applications</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
@@ -3416,17 +3468,17 @@
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Are there any related applications, previous proposals or demolitions for the site</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3435,24 +3487,20 @@
       <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Proposal completed</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -3466,99 +3514,91 @@
       <c r="B93" s="2" t="n"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
+          <t>Proposal completion date</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>A description of the related application</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n"/>
-      <c r="B94" s="2" t="n"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Related applications</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Details of any other development proposals made for the site</t>
+        </is>
+      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>Decision date</t>
-        </is>
-      </c>
+          <t>Has related applications</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr"/>
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>Are there any related applications, previous proposals or demolitions for the site</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A95" s="2" t="n"/>
+      <c r="B95" s="2" t="n"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related applications[]</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3567,19 +3607,19 @@
       <c r="B96" s="2" t="n"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related applications[]</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>A description of the related application</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -3589,7 +3629,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3598,24 +3638,24 @@
       <c r="B97" s="2" t="n"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related applications[]</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -3625,8 +3665,16 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n"/>
-      <c r="B98" s="2" t="n"/>
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -3634,24 +3682,24 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3665,24 +3713,28 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3696,19 +3748,23 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -3727,19 +3783,23 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -3758,14 +3818,18 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -3789,19 +3853,19 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -3811,37 +3875,33 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A104" s="2" t="n"/>
+      <c r="B104" s="2" t="n"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Northing</t>
+        </is>
+      </c>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3850,25 +3910,29 @@
       <c r="B105" s="2" t="n"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3877,20 +3941,24 @@
       <c r="B106" s="2" t="n"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -3900,28 +3968,32 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n"/>
-      <c r="B107" s="2" t="n"/>
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr"/>
       <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -3935,24 +4007,20 @@
       <c r="B108" s="2" t="n"/>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -3966,27 +4034,116 @@
       <c r="B109" s="2" t="n"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr"/>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n"/>
+      <c r="B110" s="2" t="n"/>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>The complete name of a person</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n"/>
+      <c r="B111" s="2" t="n"/>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n"/>
+      <c r="B112" s="2" t="n"/>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -3994,40 +4151,40 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B65"/>
-    <mergeCell ref="A34:A41"/>
-    <mergeCell ref="A42:A55"/>
-    <mergeCell ref="A24:A29"/>
+    <mergeCell ref="B44:B57"/>
+    <mergeCell ref="A107:A112"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="B84:B88"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="B94:B97"/>
+    <mergeCell ref="B98:B106"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A95:A103"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="A66:A80"/>
-    <mergeCell ref="A81:A85"/>
-    <mergeCell ref="B95:B103"/>
-    <mergeCell ref="B59:B61"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="B56"/>
-    <mergeCell ref="A91:A94"/>
-    <mergeCell ref="A65"/>
-    <mergeCell ref="B81:B85"/>
+    <mergeCell ref="B68:B83"/>
+    <mergeCell ref="A67"/>
+    <mergeCell ref="A44:A57"/>
+    <mergeCell ref="A58"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B24:B30"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="B89:B93"/>
+    <mergeCell ref="A68:A83"/>
+    <mergeCell ref="B107:B112"/>
+    <mergeCell ref="A35:A43"/>
+    <mergeCell ref="B58"/>
     <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="A104:A109"/>
-    <mergeCell ref="B24:B29"/>
-    <mergeCell ref="A56"/>
-    <mergeCell ref="B86:B90"/>
-    <mergeCell ref="B34:B41"/>
+    <mergeCell ref="A24:A30"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="B35:B43"/>
+    <mergeCell ref="B67"/>
+    <mergeCell ref="A98:A106"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="A84:A88"/>
+    <mergeCell ref="A31:A34"/>
     <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B42:B55"/>
-    <mergeCell ref="B66:B80"/>
+    <mergeCell ref="A59:A60"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B91:B94"/>
-    <mergeCell ref="A86:A90"/>
-    <mergeCell ref="B104:B109"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="A89:A93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
